--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135843075</v>
       </c>
       <c r="B2" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135842136</v>
       </c>
       <c r="B3" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135842158</v>
       </c>
       <c r="B4" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135843075</v>
+        <v>136007559</v>
       </c>
       <c r="B2" t="n">
-        <v>91972</v>
+        <v>79520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3242</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751341</v>
+        <v>751563</v>
       </c>
       <c r="R2" t="n">
-        <v>7518398</v>
+        <v>7518412</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,60 +780,60 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843075</t>
+          <t>https://artportalen.se/Sighting/136007559</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135842136</v>
+        <v>135843075</v>
       </c>
       <c r="B3" t="n">
-        <v>99082</v>
+        <v>91972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223049</v>
+        <v>3242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergsmannijoki, Bergsmannijoki, T lm</t>
+          <t>Mustalompolo, T lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751233</v>
+        <v>751341</v>
       </c>
       <c r="R3" t="n">
-        <v>7518470</v>
+        <v>7518398</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +887,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135842136</t>
+          <t>https://artportalen.se/Sighting/135843075</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135842158</v>
+        <v>135842136</v>
       </c>
       <c r="B4" t="n">
-        <v>98327</v>
+        <v>99082</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,7 +942,7 @@
         <v>751233</v>
       </c>
       <c r="R4" t="n">
-        <v>7518462</v>
+        <v>7518470</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -1009,6 +1009,118 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135842136</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135842158</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bergsmannijoki, Bergsmannijoki, T lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>751233</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7518462</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135842158</t>
         </is>
@@ -1019,6 +1131,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007559</v>
       </c>
       <c r="B2" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135843075</v>
       </c>
       <c r="B3" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135842136</v>
       </c>
       <c r="B4" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135842158</v>
       </c>
       <c r="B5" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007559</v>
       </c>
       <c r="B2" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135843075</v>
       </c>
       <c r="B3" t="n">
-        <v>91986</v>
+        <v>91987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135842136</v>
       </c>
       <c r="B4" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135842158</v>
       </c>
       <c r="B5" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135843075</v>
       </c>
       <c r="B3" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135842136</v>
       </c>
       <c r="B4" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135842158</v>
       </c>
       <c r="B5" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007559</v>
       </c>
       <c r="B2" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135843075</v>
       </c>
       <c r="B3" t="n">
-        <v>91988</v>
+        <v>91989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135842136</v>
       </c>
       <c r="B4" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135842158</v>
       </c>
       <c r="B5" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007559</v>
       </c>
       <c r="B2" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135843075</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135842136</v>
       </c>
       <c r="B4" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135842158</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007559</v>
       </c>
       <c r="B2" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135843075</v>
       </c>
       <c r="B3" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135842136</v>
       </c>
       <c r="B4" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135842158</v>
       </c>
       <c r="B5" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007559</v>
       </c>
       <c r="B2" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,7 +795,7 @@
         <v>135843075</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
+        <v>92002</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135842136</v>
       </c>
       <c r="B4" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135842158</v>
       </c>
       <c r="B5" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007559</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,7 +795,7 @@
         <v>135843075</v>
       </c>
       <c r="B3" t="n">
-        <v>92002</v>
+        <v>92009</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135842136</v>
       </c>
       <c r="B4" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135842158</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135843075</v>
       </c>
       <c r="B3" t="n">
-        <v>92009</v>
+        <v>92010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135842136</v>
       </c>
       <c r="B4" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135842158</v>
       </c>
       <c r="B5" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007559</v>
       </c>
       <c r="B2" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135843075</v>
       </c>
       <c r="B3" t="n">
-        <v>92010</v>
+        <v>92023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135842136</v>
       </c>
       <c r="B4" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135842158</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007559</v>
       </c>
       <c r="B2" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
